--- a/CS_100826/AMBITION_ANERI_CS_100826.xlsx
+++ b/CS_100826/AMBITION_ANERI_CS_100826.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pratik.SJFS\Desktop\CS_100826\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\latest\OPS-TOOL-V2\CS_100826\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C925E207-2431-4A23-9B67-320FE46DC1DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855AF862-B922-45E8-BD35-7EF7289E4674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3327,17 +3327,18 @@
   <dimension ref="A1:L551"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" customWidth="1"/>
-    <col min="5" max="5" width="2.85546875" customWidth="1"/>
-    <col min="6" max="7" width="4.42578125" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" customWidth="1"/>
-    <col min="10" max="10" width="4.5703125" customWidth="1"/>
-    <col min="11" max="11" width="6.85546875" customWidth="1"/>
-    <col min="12" max="12" width="7.42578125" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
